--- a/排课结果/特殊要求放宽记录.xlsx
+++ b/排课结果/特殊要求放宽记录.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
+          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>允许连排块 [3, 2](仅周末2天装5节)</t>
+          <t>小数分段+周末大连排 {'14403009.001@FA': '3,3', '14403009.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>小数分段+周末大连排 {'110000320.001@FA': '4,4', '110000320.001@FB': '3,3'} 守恒Σ=40=LLXS40</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 4](仅周末2天装8节)</t>
+          <t>小数分段+周末大连排 {'110000460.001@FA': '4,4', '110000460.001@FB': '3,3'} 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 4](仅周末2天装8节)</t>
+          <t>小数分段+周末大连排 {'110000460.002@FA': '4,4', '110000460.002@FB': '3,3'} 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 4](仅周末2天装8节)</t>
+          <t>小数分段+周末大连排 {'110000460.003@FA': '4,4', '110000460.003@FB': '3,3'} 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 4](仅周末2天装8节)</t>
+          <t>小数分段+周末大连排 {'110000460.004@FA': '4,4', '110000460.004@FB': '3,3'} 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 4](仅周末2天装8节)</t>
+          <t>小数分段+周末大连排 {'110000460.005@FA': '4,4', '110000460.005@FB': '3,3'} 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2366,11 +2366,7 @@
           <t>110000460.006</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>高等数学b-2</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>B</t>
@@ -2378,12 +2374,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>允许连排块 [3, 3](仅周末2天装6节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2393,11 +2389,7 @@
           <t>110000480.001</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>高等数学c-2</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>B</t>
@@ -2405,12 +2397,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>允许连排块 [3, 3](仅周末2天装6节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2420,11 +2412,7 @@
           <t>110000480.002</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>高等数学c-2</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>B</t>
@@ -2432,12 +2420,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>允许连排块 [3, 3](仅周末2天装6节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2447,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>小数分段+周末大连排 {'110000640.017@FA': '4,4', '110000640.017@FB': '3,3'} 守恒Σ=56=LLXS56</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2486,7 +2474,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 4](仅周末2天装8节)</t>
+          <t>小数分段+周末大连排 {'110000670.001@FA': '4,4', '110000670.001@FB': '3,3'} 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2501,11 +2489,7 @@
           <t>110000670.002</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>高等数学a-2</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>B</t>
@@ -2513,12 +2497,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>允许连排块 [3, 3](仅周末2天装6节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2528,11 +2512,7 @@
           <t>130000510.002</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>B</t>
@@ -2540,12 +2520,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2555,11 +2535,7 @@
           <t>130000510.004</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>B</t>
@@ -2567,12 +2543,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2582,11 +2558,7 @@
           <t>130000510.005</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>B</t>
@@ -2594,12 +2566,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2609,11 +2581,7 @@
           <t>130000510.006</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>B</t>
@@ -2621,12 +2589,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2636,11 +2604,7 @@
           <t>130000510.007</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>B</t>
@@ -2648,12 +2612,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2663,11 +2627,7 @@
           <t>130000510.008</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>B</t>
@@ -2675,12 +2635,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2690,11 +2650,7 @@
           <t>130000510.009</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>B</t>
@@ -2702,12 +2658,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2717,11 +2673,7 @@
           <t>130000510.010</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>大学物理（一）</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>B</t>
@@ -2729,12 +2681,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 3](仅周末2天装7节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2708,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>允许连排块 [3, 3](仅周末2天装6节)</t>
+          <t>小数分段+周末大连排 {'14403010.001@FA': '3,3', '14403010.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2783,7 +2735,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>允许连排块 [3, 3](仅周末2天装6节)</t>
+          <t>小数分段+周末大连排 {'17716055.001@FA': '3,3', '17716055.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2798,11 +2750,7 @@
           <t>110010321.001</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>高等代数2</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>B</t>
@@ -2810,12 +2758,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>允许连排块 [4, 4](仅周末2天装8节)</t>
+          <t>无@FA/@FB拆分，跳过</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>✅已排入</t>
+          <t>❌仍排不上</t>
         </is>
       </c>
     </row>

--- a/排课结果/特殊要求放宽记录.xlsx
+++ b/排课结果/特殊要求放宽记录.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,10 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>放宽桶</t>
+          <t>放宽内容</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>放宽内容</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>结果</t>
         </is>
@@ -456,15 +451,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -483,15 +473,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -510,15 +495,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -537,15 +517,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -564,15 +539,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -591,15 +561,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -618,15 +583,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -645,15 +605,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -672,15 +627,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -699,15 +649,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -726,15 +671,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -753,15 +693,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -780,15 +715,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -807,15 +737,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -834,15 +759,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -861,15 +781,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -888,15 +803,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -915,15 +825,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -942,15 +847,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -969,15 +869,10 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -996,15 +891,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1023,15 +913,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1050,15 +935,10 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1077,15 +957,10 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1104,15 +979,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1131,15 +1001,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1158,15 +1023,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1185,15 +1045,10 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1212,15 +1067,10 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1239,15 +1089,10 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1266,15 +1111,10 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1293,15 +1133,10 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1320,15 +1155,10 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1347,15 +1177,10 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1374,15 +1199,10 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1401,15 +1221,10 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1428,15 +1243,10 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1455,15 +1265,10 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1482,15 +1287,10 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1509,15 +1309,10 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1536,15 +1331,10 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1563,15 +1353,10 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1590,15 +1375,10 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1617,15 +1397,10 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1644,15 +1419,10 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1671,15 +1441,10 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1698,15 +1463,10 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1725,15 +1485,10 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1752,15 +1507,10 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1779,15 +1529,10 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1806,15 +1551,10 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
-        <is>
-          <t>删禁排后仍无可行位: ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>
@@ -1833,15 +1573,10 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1860,15 +1595,10 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1887,15 +1617,10 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1914,15 +1639,10 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1941,15 +1661,10 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1968,15 +1683,10 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -1995,15 +1705,10 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2022,15 +1727,10 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2049,15 +1749,10 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2076,15 +1771,10 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2103,15 +1793,10 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2130,15 +1815,10 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2157,15 +1837,10 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>删被覆盖禁排段['全周(1-2节)'] + 连排块2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
-        <is>
-          <t>删类别禁排段(L3覆盖L2): ['全周(1-2节)']</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2184,15 +1859,10 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=32=LLXS32</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'14403009.001@FA': '3,3', '14403009.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2211,15 +1881,10 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=40=LLXS40</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000320.001@FA': '4,4', '110000320.001@FB': '3,3'} 守恒Σ=40=LLXS40</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2238,15 +1903,10 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000460.001@FA': '4,4', '110000460.001@FB': '3,3'} 守恒Σ=96=LLXS96</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2265,15 +1925,10 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000460.002@FA': '4,4', '110000460.002@FB': '3,3'} 守恒Σ=96=LLXS96</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2292,15 +1947,10 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000460.003@FA': '4,4', '110000460.003@FB': '3,3'} 守恒Σ=96=LLXS96</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2319,15 +1969,10 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000460.004@FA': '4,4', '110000460.004@FB': '3,3'} 守恒Σ=96=LLXS96</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2346,15 +1991,10 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000460.005@FA': '4,4', '110000460.005@FB': '3,3'} 守恒Σ=96=LLXS96</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2366,20 +2006,19 @@
           <t>110000460.006</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>高等数学b-2</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2389,20 +2028,19 @@
           <t>110000480.001</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>高等数学c-2</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2412,20 +2050,19 @@
           <t>110000480.002</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>高等数学c-2</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2079,10 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=56=LLXS56</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000640.017@FA': '4,4', '110000640.017@FB': '3,3'} 守恒Σ=56=LLXS56</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2469,15 +2101,10 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=96=LLXS96</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'110000670.001@FA': '4,4', '110000670.001@FB': '3,3'} 守恒Σ=96=LLXS96</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2489,20 +2116,19 @@
           <t>110000670.002</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>高等数学a-2</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2512,20 +2138,19 @@
           <t>130000510.002</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2535,20 +2160,19 @@
           <t>130000510.004</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2558,20 +2182,19 @@
           <t>130000510.005</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2581,20 +2204,19 @@
           <t>130000510.006</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2604,20 +2226,19 @@
           <t>130000510.007</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2627,20 +2248,19 @@
           <t>130000510.008</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2650,20 +2270,19 @@
           <t>130000510.009</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2673,20 +2292,19 @@
           <t>130000510.010</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>大学物理（一）</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[4, 3]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>❌仍排不上</t>
+          <t>✅已排入</t>
         </is>
       </c>
     </row>
@@ -2703,15 +2321,10 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>小数分段+连排放宽 守恒Σ=32=LLXS32</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'14403010.001@FA': '3,3', '14403010.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2720,25 +2333,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>17716055.001</t>
+          <t>15ALT016.003</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>短视频平台运营与用户增长</t>
+          <t>队田径业余队</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>删被覆盖禁排段[] + 连排块[3, 3]</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
-        <is>
-          <t>小数分段+周末大连排 {'17716055.001@FA': '3,3', '17716055.001@FB': '2,2'} 守恒Σ=32=LLXS32</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
         <is>
           <t>✅已排入</t>
         </is>
@@ -2747,21 +2355,460 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>17716055.001</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>短视频平台运营与用户增长</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>小数分段+连排放宽 守恒Σ=32=LLXS32</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>✅已排入</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>110010321.001</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>无@FA/@FB拆分，跳过</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>高等代数2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>删被覆盖禁排段[] + 连排块[4, 4]</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>✅已排入</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>150130580.002</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>150130580.003</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>150130580.004</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>150130580.005</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>150130580.006</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=64)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>150130580.007</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>150130580.008</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>专项4</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>150130680.002</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>150130680.003</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>150130680.004</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>150130680.005</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=96)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>150130680.006</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>专项2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=96)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>150140670.002</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>专项3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>150140670.003</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>专项3</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>150140670.004</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>专项3</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>@FA/@FB放宽后仍无解或不守恒(got=0,T=64)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>150140760.002</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>专项5</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>150140760.003</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>专项5</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>150140760.004</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>专项5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>❌仍排不上</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>151130120.001</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>乒乓球</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>删禁排[]后仍无可行位</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
         <is>
           <t>❌仍排不上</t>
         </is>

--- a/排课结果/特殊要求放宽记录.xlsx
+++ b/排课结果/特殊要求放宽记录.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>删禁排['全周(1-2节)']后仍无可行位</t>
+          <t>删禁排['全周(1-2节)']后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>删禁排[]后仍无可行位</t>
+          <t>删禁排[]后仍无可行位(含最小偏离)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
